--- a/summary_eval_diff_data.xlsx
+++ b/summary_eval_diff_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22500"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="859">
   <si>
     <t>query</t>
   </si>
@@ -11078,6 +11078,20 @@
   </si>
   <si>
     <t>跑步</t>
+  </si>
+  <si>
+    <t>2025年02月16日19时17分户外跑步最快配速为6分0秒/公里
+2025年02月16日19时17分户外跑步配速为6分27秒/公里
+2025年02月16日19时17分户外跑步步数为6306步
+2025年02月16日19时17分户外跑步热量为391千卡
+2025年02月16日19时17分户外跑步最大步频为197步/分钟
+2025年02月16日19时17分户外跑步步频为176步/分钟
+2025年02月16日19时17分户外跑步用时为35分38秒
+2025年02月16日跑力指数为35.99
+2025年02月16日19时17分户外跑步最大心率为163次/分钟
+2025年02月16日19时17分户外跑步心率为142次/分钟
+2025年02月16日19时17分户外跑步距离为5.52千米
+2025年02月16日19时17分户外跑步速度为9.29公里/小时</t>
   </si>
   <si>
     <t xml:space="preserve">2025年02月16日19时17分户外跑步最快配速为6分0秒/公里
@@ -15011,12 +15025,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -15554,7 +15571,10 @@
   <dimension ref="A1:N128"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="11" width="10.3846153846154" style="1"/>
+    <col min="1" max="5" width="10.3846153846154" style="1"/>
+    <col min="6" max="6" width="78.1923076923077" style="1" customWidth="1"/>
+    <col min="7" max="7" width="91.0192307692308" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.3846153846154" style="1"/>
     <col min="12" max="12" width="118.269230769231" style="1" customWidth="1"/>
     <col min="13" max="16384" width="10.3846153846154" style="1"/>
   </cols>
@@ -19968,7 +19988,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" ht="409.5" spans="1:14">
       <c r="A110" s="1" t="s">
         <v>722</v>
       </c>
@@ -19984,34 +20004,34 @@
       <c r="E110" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F110" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>725</v>
+      <c r="G110" s="2" t="s">
+        <v>726</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>32</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>26</v>
@@ -20026,22 +20046,22 @@
         <v>724</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>23</v>
@@ -20052,7 +20072,7 @@
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>26</v>
@@ -20067,33 +20087,33 @@
         <v>724</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>75</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>90</v>
@@ -20108,33 +20128,33 @@
         <v>724</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>32</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>15</v>
@@ -20149,22 +20169,22 @@
         <v>724</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>75</v>
@@ -20175,7 +20195,7 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>15</v>
@@ -20190,33 +20210,33 @@
         <v>724</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>32</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>15</v>
@@ -20231,22 +20251,22 @@
         <v>724</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>32</v>
@@ -20257,7 +20277,7 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>99</v>
@@ -20272,25 +20292,25 @@
         <v>724</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>569</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>75</v>
@@ -20301,7 +20321,7 @@
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>99</v>
@@ -20316,36 +20336,36 @@
         <v>724</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>569</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>75</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>99</v>
@@ -20360,36 +20380,36 @@
         <v>724</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J119" s="1" t="s">
         <v>569</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>75</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>90</v>
@@ -20404,30 +20424,30 @@
         <v>724</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>569</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>75</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>15</v>
@@ -20439,25 +20459,25 @@
         <v>213</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>23</v>
@@ -20468,7 +20488,7 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>99</v>
@@ -20480,25 +20500,25 @@
         <v>213</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>32</v>
@@ -20509,7 +20529,7 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>15</v>
@@ -20521,25 +20541,25 @@
         <v>213</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M123" s="1" t="s">
         <v>32</v>
@@ -20550,7 +20570,7 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>15</v>
@@ -20562,25 +20582,25 @@
         <v>213</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>32</v>
@@ -20591,7 +20611,7 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>99</v>
@@ -20603,36 +20623,36 @@
         <v>213</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>23</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>15</v>
@@ -20644,25 +20664,25 @@
         <v>149</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>32</v>
@@ -20673,7 +20693,7 @@
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>15</v>
@@ -20685,30 +20705,30 @@
         <v>388</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>32</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>15</v>
@@ -20720,25 +20740,25 @@
         <v>149</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>23</v>

--- a/summary_eval_diff_data.xlsx
+++ b/summary_eval_diff_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="22500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="859">
   <si>
     <t>query</t>
   </si>
@@ -15025,15 +15025,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -15571,7 +15568,9 @@
   <dimension ref="A1:N128"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="5" width="10.3846153846154" style="1"/>
+    <col min="1" max="3" width="10.3846153846154" style="1"/>
+    <col min="4" max="4" width="25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.3846153846154" style="1"/>
     <col min="6" max="6" width="78.1923076923077" style="1" customWidth="1"/>
     <col min="7" max="7" width="91.0192307692308" style="1" customWidth="1"/>
     <col min="8" max="11" width="10.3846153846154" style="1"/>
@@ -19988,7 +19987,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="110" ht="409.5" spans="1:14">
+    <row r="110" s="1" customFormat="1" spans="1:14">
       <c r="A110" s="1" t="s">
         <v>722</v>
       </c>
@@ -20004,10 +20003,10 @@
       <c r="E110" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="F110" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="G110" s="1" t="s">
         <v>726</v>
       </c>
       <c r="H110" s="1" t="s">
@@ -20167,9 +20166,6 @@
       </c>
       <c r="E114" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>726</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>726</v>
